--- a/Historical/1991/1991_Season_Stats.xlsx
+++ b/Historical/1991/1991_Season_Stats.xlsx
@@ -979,7 +979,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Note: Some TB column values in the source don't sum cleanly to the visible 1B/2B/3B/HR breakdown — preserved as printed. Some narrow columns (HBP, SB, SAC, GP) had reading challenges for a few players; values are best-effort.</t>
+          <t>Note: Original 1991 source has 18 stat columns including K% between K and SB. Earlier transcription dropped the K% header label but left the K% values, which shifted SB/SAC/TB/E by one position. Header relabeled (2026-04-27) so the actual SB column reads correctly; E (errors) is no longer carried — its values were never preserved by the original transcription. Some TB column values still don't sum cleanly to the visible 1B/2B/3B/HR breakdown — preserved as printed. Some narrow columns (HBP, SB, SAC, GP) had reading challenges for a few players; values are best-effort.</t>
         </is>
       </c>
     </row>
@@ -1041,22 +1041,22 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>K%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>SB</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SAC</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>TB</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
